--- a/output/pdf_financials_xlsx/SGN.xlsx
+++ b/output/pdf_financials_xlsx/SGN.xlsx
@@ -6785,19 +6785,19 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>1.012875</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="N91" s="1" t="inlineStr">
         <is>
@@ -11609,7 +11609,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -16458,7 +16462,11 @@
           <t>Foreign currency translation reserve (194,204)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGN.xlsx
+++ b/output/pdf_financials_xlsx/SGN.xlsx
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.217466</v>
+        <v>3.968773</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.673394</v>
+        <v>2.88389</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>2.018054</v>
+        <v>-0.733253</v>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000365</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001062</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.000957</v>
@@ -2049,23 +2049,19 @@
         <v>136.86</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>171.3375</v>
+        <v>124.948235</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>138.353846</v>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>124.948235</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>124.948235</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>62.474118</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>62.474118</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2105,10 +2101,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.497633</v>
+        <v>-0.497998</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.572964</v>
+        <v>-1.574026</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.476906</v>
@@ -2229,10 +2225,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.497633</v>
+        <v>-0.497998</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.572964</v>
+        <v>-1.574026</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.476906</v>
@@ -2512,10 +2508,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.028552</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.06524000000000001</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -2523,19 +2519,19 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.399099</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.775</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.114</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.273</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2548,10 +2544,10 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.243</v>
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
@@ -2660,10 +2656,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.028552</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.06524000000000001</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2671,19 +2667,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.399099</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.775</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.114</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.273</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -2696,10 +2692,10 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.243</v>
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
@@ -3548,10 +3544,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.066413</v>
+        <v>0.037861</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.112533</v>
+        <v>0.047293</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -3559,19 +3555,19 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.595668</v>
+        <v>0.196569</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.507</v>
+        <v>0.458</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>14.593</v>
+        <v>11.818</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>6.92</v>
+        <v>5.806</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.155</v>
+        <v>0.882</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -3584,10 +3580,10 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.526</v>
+        <v>0.426</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.677</v>
+        <v>0.434</v>
       </c>
       <c r="N48" s="1" t="inlineStr">
         <is>
@@ -9631,7 +9627,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12167,7 +12163,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
@@ -14432,7 +14428,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -31078,7 +31074,11 @@
           <t>Cash paid for reclamation deposits 3</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -63820,7 +63820,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -63884,10 +63884,10 @@
         </is>
       </c>
       <c r="Q545" s="5" t="n">
-        <v>-3.968773</v>
+        <v>3.968773</v>
       </c>
       <c r="R545" s="5" t="n">
-        <v>-2.88389</v>
+        <v>2.88389</v>
       </c>
       <c r="S545" t="inlineStr">
         <is>
@@ -68275,7 +68275,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -79258,7 +79258,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -81153,7 +81153,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E720" s="5" t="n">

--- a/output/pdf_financials_xlsx/SGN.xlsx
+++ b/output/pdf_financials_xlsx/SGN.xlsx
@@ -8091,19 +8091,19 @@
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.176915</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>0.07994999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -23525,7 +23525,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -28246,7 +28250,11 @@
           <t>Proceeds from disposal of property, plant and equipment 4</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
